--- a/Abgabe/BOM.xlsx
+++ b/Abgabe/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Documents\Uni\Semester 6\Projektarbeit\active-balancing\Abgabe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB18F601-B1B6-45DB-AE8F-40CDFD12D8A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D72F85D-05E6-4DB5-BB4F-E3A2DFD777DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{5DC78B72-9050-47CC-A50E-560609C3D48D}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{5DC78B72-9050-47CC-A50E-560609C3D48D}"/>
   </bookViews>
   <sheets>
     <sheet name="Aktive_Bal_Doppelmosfet" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="198">
   <si>
     <t>Reference</t>
   </si>
@@ -167,9 +167,6 @@
     <t>Diode_SMD:D_SMA</t>
   </si>
   <si>
-    <t>http://www.vishay.com/docs/88525/1n5817.pdf</t>
-  </si>
-  <si>
     <t>FL1</t>
   </si>
   <si>
@@ -179,9 +176,6 @@
     <t>Aktive_Bal_Footprints:common mode choke foot</t>
   </si>
   <si>
-    <t>https://productfinder.pulseelectronics.com/api/open/product-attachments/datasheet/ph9455.105nl</t>
-  </si>
-  <si>
     <t>J1</t>
   </si>
   <si>
@@ -200,9 +194,6 @@
     <t>Aktive_Bal_Footprints:ASSMANN_A-DF_09_A_KG-T4S</t>
   </si>
   <si>
-    <t>file://C:\Users\maria\Documents\Uni\Semester 6\Projektarbeit\active-balancing\KiCad\Aktive_Bal_Bericht - V4\Datasheets\sub d buchse ASS_4888_CO.pdf</t>
-  </si>
-  <si>
     <t>J3,J4,J5,J6,J9,J10,J11,J12,J13,J14,J21,J22,J23,J24</t>
   </si>
   <si>
@@ -516,16 +507,166 @@
   </si>
   <si>
     <t>http://www.ti.com/lit/ds/symlink/lm2596.pdf</t>
+  </si>
+  <si>
+    <t>Bestellte Stückzahl</t>
+  </si>
+  <si>
+    <t>Stückpreis bei Großmengen</t>
+  </si>
+  <si>
+    <t>https://yageogroup.com/content/datasheet/asset/file/KEM_C1002_X7R_SMD</t>
+  </si>
+  <si>
+    <t>https://mm.digikey.com/Volume0/opasdata/d220001/medias/docus/609/CL21B104KBCNNN_Spec.pdf</t>
+  </si>
+  <si>
+    <t>Kosten für bestellte Stückzahl</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/865080342006.pdf</t>
+  </si>
+  <si>
+    <t>https://mm.digikey.com/Volume0/opasdata/d220001/medias/docus/609/CL21C101JBANNNC_Spec.pdf</t>
+  </si>
+  <si>
+    <t>https://mm.digikey.com/Volume0/opasdata/d220001/medias/docus/41/CL21A475KAQNNNE_Spec.pdf</t>
+  </si>
+  <si>
+    <t>https://mm.digikey.com/Volume0/opasdata/d220001/medias/docus/926/CL_Series_MLCC_ds.pdf</t>
+  </si>
+  <si>
+    <t>https://datasheets.kyocera-avx.com/TAJ.pdf</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/875116152001.pdf</t>
+  </si>
+  <si>
+    <t>https://cdn-reichelt.de/documents/datenblatt/B300/GRM21BD72A225K.pdf</t>
+  </si>
+  <si>
+    <t>https://cdn-reichelt.de/documents/datenblatt/B300/KEM_C0XXX_X7R_DB-EN.pdf</t>
+  </si>
+  <si>
+    <t>https://mm.digikey.com/Volume0/opasdata/d220001/medias/docus/609/CL21B105KBFNNNE_Spec.pdf</t>
+  </si>
+  <si>
+    <t>https://industrial.panasonic.com/cdbs/www-data/pdf/RDE0000/ABA0000C1145.pdf</t>
+  </si>
+  <si>
+    <t>Produktlink</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/diodes-incorporated/B340A-13-F/725015</t>
+  </si>
+  <si>
+    <t>https://www.diodes.com/assets/Datasheets/ds30891.pdf</t>
+  </si>
+  <si>
+    <t>https://www.reichelt.de/de/de/shop/produkt/smd-vielschicht_0805_1_nf_x7r_10_100v_125_c-207060</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/samsung-electro-mechanics/CL21B104KBCNNNC/3886661?s=N4IgTCBcDaIMIBkwEYBCyAMAWA0quAckXCALoC%2BQA</t>
+  </si>
+  <si>
+    <t>https://www.reichelt.de/de/de/shop/produkt/mlcc_0805_2_2_f_100_v_-10_x7t-409189</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/w%C3%BCrth-elektronik/865080342006/5728011?s=N4IgTCBcDaIBwDYCsAGOKDMAWMKUJAF0BfIA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/samsung-electro-mechanics/CL21C101JBANNNC/3886672?s=N4IgTCBcDaIMIBkwEY7IAzIFICECCAckXCALoC%2BQA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/samsung-electro-mechanics/CL21A475KAQNNNE/3886902?s=N4IgTCBcDaIMIBkwEYCCAWA7AVgNKoEUA5EgURAF0BfIA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/w%C3%BCrth-elektronik/875116152001/8556651?s=N4IgTCBcDaIBwHYCsBGFA2FSwAYcpAF0BfIA</t>
+  </si>
+  <si>
+    <t>Anmerkungen</t>
+  </si>
+  <si>
+    <t>Footprint überprüfen</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/kyocera-avx/TAJP106M010RNJ/929913?s=N4IgTCBcDaICoEEBSAFAjABgGwFkOYCUA5JEAXQF8g</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/samsung-electro-mechanics/CL21B106KOQNNNE/3888530?s=N4IgTCBcDaIMIBkwEYBCyAMA2A0geQEUA5EgURAF0BfIA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/samsung-electro-mechanics/CL21B105KBFNNNE/3886687?s=N4IgTCBcDaIMIBkwEYBCyAMBWA0qgYgHLECiIAugL5A</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/panasonic-industry/EEE-1CA471UP/766059?s=N4IgTCBcDaIKIILQEYDCBBALAdmQVQAUQBdAXyA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/kemet/C0805C103K5RACTU/411157?s=N4IgTCBcDaIMIAYAcCCscCMCDMBpVASgIJwAqAqiALoC%2BQA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/traco-power/TCK-050/9382114?s=N4IgTCBcDaICoGEDSBaADAVjSAugXyA</t>
+  </si>
+  <si>
+    <t>https://www.mouser.de/datasheet/3/1230/1/tck_050_datasheet.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/w%C3%BCrth-elektronik/691137710002/6644051?s=N4IgTCBcDaIGwE4CMSDMB2dSAMuIF0BfIA</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/691137710002.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.at/de/products/detail/assmann-wsw-components/A-DF-09-A-KG-T4S/1241802</t>
+  </si>
+  <si>
+    <t>https://www.assmann-wsw.com/uploads/datasheets/ASS_4888_CO.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.at/de/products/detail/sullins-connector-solutions/PPTC021LFBN-RC/810142?s=N4IgTCBcDaIApwCoGEAMYCMAZAYgIQDkBaAJWRAF0BfIA</t>
+  </si>
+  <si>
+    <t>https://mm.digikey.com/Volume0/opasdata/d220001/medias/docus/937/Female_Headers.100_DS.pdf</t>
+  </si>
+  <si>
+    <t>https://www.reichelt.de/de/de/shop/produkt/36pol_stiftleiste_gerade_rm_2_54-19504</t>
+  </si>
+  <si>
+    <t>https://cdn-reichelt.de/documents/datenblatt/C140/SL%201X36G%202,54.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/w%C3%BCrth-elektronik/691214110003/2508517</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/691214110003.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/taiyo-yuden/NRS6045T100MMGK/2665984</t>
+  </si>
+  <si>
+    <t>https://mm.digikey.com/Volume0/opasdata/d220001/medias/docus/7087/NR-H-S-V%20Datasheet.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;€&quot;;[Red]\-#,##0\ &quot;€&quot;"/>
+    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -548,17 +689,38 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="12">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -595,8 +757,8 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExterneDaten_1" connectionId="1" xr16:uid="{C8206F66-10A1-47FE-97AA-9AE5CB2C8107}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="9">
-    <queryTableFields count="8">
+  <queryTableRefresh nextId="14" unboundColumnsRight="5">
+    <queryTableFields count="13">
       <queryTableField id="1" name="Reference" tableColumnId="1"/>
       <queryTableField id="2" name="Qty" tableColumnId="2"/>
       <queryTableField id="3" name="Value" tableColumnId="3"/>
@@ -605,23 +767,33 @@
       <queryTableField id="6" name="Exclude from Board" tableColumnId="6"/>
       <queryTableField id="7" name="Footprint" tableColumnId="7"/>
       <queryTableField id="8" name="Datasheet" tableColumnId="8"/>
+      <queryTableField id="9" dataBound="0" tableColumnId="9"/>
+      <queryTableField id="10" dataBound="0" tableColumnId="10"/>
+      <queryTableField id="11" dataBound="0" tableColumnId="11"/>
+      <queryTableField id="12" dataBound="0" tableColumnId="12"/>
+      <queryTableField id="13" dataBound="0" tableColumnId="13"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FF99C66-B9A5-4B58-9A2D-91EE9E944E95}" name="Aktive_Bal_Doppelmosfet" displayName="Aktive_Bal_Doppelmosfet" ref="A1:H55" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:H55" xr:uid="{5FF99C66-B9A5-4B58-9A2D-91EE9E944E95}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{8245B2B7-4876-4526-87C1-E7CF70920112}" uniqueName="1" name="Reference" queryTableFieldId="1" dataDxfId="6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FF99C66-B9A5-4B58-9A2D-91EE9E944E95}" name="Aktive_Bal_Doppelmosfet" displayName="Aktive_Bal_Doppelmosfet" ref="A1:M55" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:M55" xr:uid="{5FF99C66-B9A5-4B58-9A2D-91EE9E944E95}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{8245B2B7-4876-4526-87C1-E7CF70920112}" uniqueName="1" name="Reference" queryTableFieldId="1" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{981E7317-D2AF-408E-8673-F2F6BCB12F70}" uniqueName="2" name="Qty" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{B64E8B8E-964B-4B4D-B734-5E9C6F4C3E8C}" uniqueName="3" name="Value" queryTableFieldId="3" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{D7B53A40-562C-4807-B87B-53791F50E2BF}" uniqueName="4" name="DNP" queryTableFieldId="4" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{1BEA039B-C35B-4213-9F34-5D208A07F254}" uniqueName="5" name="Exclude from BOM" queryTableFieldId="5" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{FFE0290A-A9E5-4D86-B68C-2D80E68D8CE3}" uniqueName="6" name="Exclude from Board" queryTableFieldId="6" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{C3261637-00F6-47DC-AF4B-CDA7F1981624}" uniqueName="7" name="Footprint" queryTableFieldId="7" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{4A508BD9-A197-46BE-B7A5-E588037350E1}" uniqueName="8" name="Datasheet" queryTableFieldId="8" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{B64E8B8E-964B-4B4D-B734-5E9C6F4C3E8C}" uniqueName="3" name="Value" queryTableFieldId="3" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{D7B53A40-562C-4807-B87B-53791F50E2BF}" uniqueName="4" name="DNP" queryTableFieldId="4" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{1BEA039B-C35B-4213-9F34-5D208A07F254}" uniqueName="5" name="Exclude from BOM" queryTableFieldId="5" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{FFE0290A-A9E5-4D86-B68C-2D80E68D8CE3}" uniqueName="6" name="Exclude from Board" queryTableFieldId="6" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{C3261637-00F6-47DC-AF4B-CDA7F1981624}" uniqueName="7" name="Footprint" queryTableFieldId="7" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{4A508BD9-A197-46BE-B7A5-E588037350E1}" uniqueName="8" name="Datasheet" queryTableFieldId="8" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{02950607-75AE-47A5-A5AC-90FD5A67C0BE}" uniqueName="9" name="Bestellte Stückzahl" queryTableFieldId="9" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{1DE22A2B-A633-407B-A006-75CDF02B14A4}" uniqueName="10" name="Kosten für bestellte Stückzahl" queryTableFieldId="10" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{96C0C7FA-01E1-410B-B098-40B2D24D9C97}" uniqueName="11" name="Stückpreis bei Großmengen" queryTableFieldId="11" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{1CD0DD19-A55A-4B28-8AB6-2049101ECE36}" uniqueName="12" name="Produktlink" queryTableFieldId="12" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{B0EED120-F1DF-4977-BB5B-E9CB0D00DB1E}" uniqueName="13" name="Anmerkungen" queryTableFieldId="13" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -944,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C70F1DE3-F6FC-4523-A997-2EF5AF24F92B}">
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="80.7265625" bestFit="1" customWidth="1"/>
@@ -954,9 +1126,14 @@
     <col min="5" max="5" width="18.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.26953125" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="80.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.36328125" customWidth="1"/>
+    <col min="10" max="10" width="31.54296875" customWidth="1"/>
+    <col min="11" max="11" width="30.54296875" customWidth="1"/>
+    <col min="12" max="12" width="142.7265625" customWidth="1"/>
+    <col min="13" max="13" width="29.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -981,8 +1158,23 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J1" t="s">
+        <v>156</v>
+      </c>
+      <c r="K1" t="s">
+        <v>153</v>
+      </c>
+      <c r="L1" t="s">
+        <v>167</v>
+      </c>
+      <c r="M1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1005,10 +1197,23 @@
         <v>11</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>164</v>
+      </c>
+      <c r="I2" s="1">
+        <v>20</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1031,10 +1236,23 @@
         <v>11</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+      <c r="I3" s="1">
+        <v>50</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1.08</v>
+      </c>
+      <c r="K3" s="2">
+        <v>1.153E-2</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1057,10 +1275,23 @@
         <v>11</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>163</v>
+      </c>
+      <c r="I4" s="1">
+        <v>10</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -1083,10 +1314,23 @@
         <v>18</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>157</v>
+      </c>
+      <c r="I5" s="1">
+        <v>10</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="K5" s="2">
+        <v>9.1090000000000004E-2</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
@@ -1109,10 +1353,23 @@
         <v>11</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>158</v>
+      </c>
+      <c r="I6" s="1">
+        <v>10</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.34</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1.298E-2</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="M6" s="1"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
@@ -1135,10 +1392,23 @@
         <v>11</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>159</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.18</v>
+      </c>
+      <c r="K7" s="2">
+        <v>2.3429999999999999E-2</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="M7" s="1"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -1160,11 +1430,26 @@
       <c r="G8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H8" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1.09226</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -1187,10 +1472,23 @@
         <v>11</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+      <c r="I9" s="1">
+        <v>10</v>
+      </c>
+      <c r="J9" s="2">
+        <v>3.04</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0.33673999999999998</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="M9" s="1"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -1213,10 +1511,23 @@
         <v>11</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>160</v>
+      </c>
+      <c r="I10" s="1">
+        <v>10</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K10" s="2">
+        <v>5.8380000000000001E-2</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="M10" s="1"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -1239,10 +1550,23 @@
         <v>11</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>165</v>
+      </c>
+      <c r="I11" s="1">
+        <v>10</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.54</v>
+      </c>
+      <c r="K11" s="2">
+        <v>2.375E-2</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="M11" s="1"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>30</v>
       </c>
@@ -1265,10 +1589,25 @@
         <v>32</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <v>166</v>
+      </c>
+      <c r="I12" s="1">
+        <v>2</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1.24</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0.23305999999999999</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
@@ -1291,10 +1630,23 @@
         <v>11</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+        <v>154</v>
+      </c>
+      <c r="I13" s="1">
+        <v>10</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0.51</v>
+      </c>
+      <c r="K13" s="2">
+        <v>2.332E-2</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="M13" s="1"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
@@ -1316,149 +1668,227 @@
       <c r="G14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0.82</v>
+      </c>
+      <c r="K14" s="2">
+        <v>9.4579999999999997E-2</v>
+      </c>
+      <c r="L14" t="s">
+        <v>168</v>
+      </c>
+      <c r="M14" s="1"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2</v>
+      </c>
+      <c r="J15" s="2">
+        <v>10.54</v>
+      </c>
+      <c r="K15" s="3">
+        <v>3.17</v>
+      </c>
+      <c r="L15" t="s">
+        <v>184</v>
+      </c>
+      <c r="M15" s="1"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
+      <c r="D16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1" t="s">
+      <c r="H16" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="I16" s="1">
+        <v>2</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="K16" s="2">
+        <v>0.22717999999999999</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="M16" s="1"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="1" t="s">
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
+      <c r="D17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="H17" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I17" s="1">
+        <v>2</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="K17" s="2">
+        <v>0.37917000000000001</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="M17" s="1"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="B18">
         <v>14</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I18" s="1">
+        <v>20</v>
+      </c>
+      <c r="J18" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="K18" s="2">
+        <v>0.12018</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="M18" s="1"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="1" t="s">
+      <c r="D19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
+      <c r="H19" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="I19" s="1">
+        <v>5</v>
+      </c>
+      <c r="J19" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M19" s="1"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="B20">
         <v>6</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
@@ -1470,21 +1900,34 @@
         <v>10</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+        <v>195</v>
+      </c>
+      <c r="I20" s="1">
+        <v>12</v>
+      </c>
+      <c r="J20" s="2">
+        <v>5.98</v>
+      </c>
+      <c r="K20" s="2">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="M20" s="1"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B21">
         <v>3</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
@@ -1496,21 +1939,34 @@
         <v>10</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="K21" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M21" s="1"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
@@ -1522,15 +1978,28 @@
         <v>10</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="K22" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M22" s="1"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -1548,15 +2017,28 @@
         <v>10</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+      <c r="I23" s="1">
+        <v>2</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0.48</v>
+      </c>
+      <c r="K23" s="2">
+        <v>0.128</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="M23" s="1"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -1574,47 +2056,57 @@
         <v>10</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
+      <c r="H25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="B26">
         <v>32</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>10</v>
@@ -1626,203 +2118,243 @@
         <v>10</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B27">
         <v>4</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" s="1" t="s">
+      <c r="D28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="B29">
         <v>35</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="1" t="s">
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32" s="1" t="s">
+      <c r="D33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="B34">
         <v>16</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>10</v>
@@ -1834,73 +2366,88 @@
         <v>10</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B35">
         <v>32</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
+      <c r="H36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="B37">
         <v>4</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>10</v>
@@ -1912,484 +2459,590 @@
         <v>10</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B38">
         <v>3</v>
       </c>
       <c r="C38" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="1" t="s">
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B39">
-        <v>1</v>
-      </c>
-      <c r="C39" s="1" t="s">
+      <c r="D40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="1" t="s">
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-      <c r="C40" s="1" t="s">
+      <c r="D41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="1" t="s">
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B41">
-        <v>1</v>
-      </c>
-      <c r="C41" s="1" t="s">
+      <c r="D42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A43" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A42" s="1" t="s">
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B42">
-        <v>1</v>
-      </c>
-      <c r="C42" s="1" t="s">
+      <c r="D43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" s="1" t="s">
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B43">
-        <v>1</v>
-      </c>
-      <c r="C43" s="1" t="s">
+      <c r="D44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A44" s="1" t="s">
+      <c r="H44" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A45" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B44">
-        <v>1</v>
-      </c>
-      <c r="C44" s="1" t="s">
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G44" s="1" t="s">
+      <c r="D45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H44" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" s="1" t="s">
+      <c r="H45" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B45">
-        <v>1</v>
-      </c>
-      <c r="C45" s="1" t="s">
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A46" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G45" s="1" t="s">
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="D46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A46" s="1" t="s">
+      <c r="H46" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B46">
-        <v>1</v>
-      </c>
-      <c r="C46" s="1" t="s">
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A47" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G46" s="1" t="s">
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="D47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
+      <c r="H47" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B47">
-        <v>1</v>
-      </c>
-      <c r="C47" s="1" t="s">
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A48" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" s="1" t="s">
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="D48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" s="1" t="s">
+      <c r="H48" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B48">
-        <v>1</v>
-      </c>
-      <c r="C48" s="1" t="s">
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" s="1" t="s">
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="D49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
+      <c r="H49" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B49">
-        <v>1</v>
-      </c>
-      <c r="C49" s="1" t="s">
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G49" s="1" t="s">
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="D50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50" s="1" t="s">
+      <c r="H50" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B50">
-        <v>1</v>
-      </c>
-      <c r="C50" s="1" t="s">
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A51" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G50" s="1" t="s">
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="D51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" s="1" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A51" s="1" t="s">
+      <c r="H51" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B51">
-        <v>1</v>
-      </c>
-      <c r="C51" s="1" t="s">
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A52" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G51" s="1" t="s">
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="D52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H52" s="1" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A52" s="1" t="s">
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A53" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="B52">
-        <v>1</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A53" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="B53">
         <v>4</v>
       </c>
       <c r="C53" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A54" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G53" s="1" t="s">
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="D54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A54" s="1" t="s">
+      <c r="H54" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B54">
-        <v>1</v>
-      </c>
-      <c r="C54" s="1" t="s">
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A55" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G54" s="1" t="s">
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="D55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A55" s="1" t="s">
+      <c r="H55" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B55">
-        <v>1</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>154</v>
-      </c>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H14" r:id="rId1" xr:uid="{B78A06F1-FCAD-42EF-83AC-9F4500B30A01}"/>
+    <hyperlink ref="H8" r:id="rId2" xr:uid="{D6DE0464-CB78-481C-BEB7-176FBFE3824F}"/>
+    <hyperlink ref="L8" r:id="rId3" xr:uid="{FB217714-44C2-499F-8E3B-7DEB896883FA}"/>
+    <hyperlink ref="L10" r:id="rId4" xr:uid="{1038D90E-7EAF-478C-BF78-787C20314349}"/>
+    <hyperlink ref="L13" r:id="rId5" xr:uid="{1D0A81BC-0637-4D51-8393-F8B7623C9AAA}"/>
+    <hyperlink ref="H17" r:id="rId6" xr:uid="{E7367157-7510-4C01-BBC8-A9BBF4E9B366}"/>
+    <hyperlink ref="L19" r:id="rId7" xr:uid="{EC612383-17BE-4B44-B2ED-1B82FB019128}"/>
+    <hyperlink ref="L21" r:id="rId8" xr:uid="{FE7EC3EF-4FA4-4C36-BA3D-754D087BC864}"/>
+    <hyperlink ref="L22" r:id="rId9" xr:uid="{79CA8F48-A562-40AB-920C-FEB1BE5784DB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId10"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Abgabe/BOM.xlsx
+++ b/Abgabe/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Documents\Uni\Semester 6\Projektarbeit\active-balancing\Abgabe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D72F85D-05E6-4DB5-BB4F-E3A2DFD777DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191ED42D-0D29-4448-BEA9-9BEB57A8959F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{5DC78B72-9050-47CC-A50E-560609C3D48D}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Tabelle1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="ExterneDaten_1" localSheetId="0" hidden="1">Aktive_Bal_Doppelmosfet!$A$1:$H$55</definedName>
+    <definedName name="ExterneDaten_1" localSheetId="0" hidden="1">Aktive_Bal_Doppelmosfet!$A$1:$H$56</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="253">
   <si>
     <t>Reference</t>
   </si>
@@ -413,9 +413,6 @@
     <t>Aktive_Bal_Footprints:SCW20C-12</t>
   </si>
   <si>
-    <t>file://C:\Users\maria\Documents\Uni\Semester 6\Projektarbeit\active-balancing\KiCad\Aktive_Bal_Bericht - V4\Datasheets\SCW20C-12.pdf</t>
-  </si>
-  <si>
     <t>U5</t>
   </si>
   <si>
@@ -425,9 +422,6 @@
     <t>Aktive_Bal_Footprints:EC1SA16N</t>
   </si>
   <si>
-    <t>file://C:\Users\maria\Documents\Uni\Semester 6\Projektarbeit\active-balancing\KiCad\Aktive_Bal_Bericht - V4\Datasheets\EC1SAN.pdf</t>
-  </si>
-  <si>
     <t>U6</t>
   </si>
   <si>
@@ -482,9 +476,6 @@
     <t>Aktive_Bal_Footprints:SOIC254P1016X460-16N</t>
   </si>
   <si>
-    <t>file://C:\Users\maria\Documents\Uni\Semester 6\Projektarbeit\active-balancing\KiCad\Aktive_Bal_Bericht - V4\Datasheets\LTV-8X7 series Rev.S.PDF</t>
-  </si>
-  <si>
     <t>U14</t>
   </si>
   <si>
@@ -645,6 +636,180 @@
   </si>
   <si>
     <t>https://mm.digikey.com/Volume0/opasdata/d220001/medias/docus/7087/NR-H-S-V%20Datasheet.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/bourns-inc/SRR1280-470M/1970000?s=N4IgTCBcDaIMoCUEEYwA4AMBaALAdgwFkQBdAXyA</t>
+  </si>
+  <si>
+    <t>https://www.bourns.com/docs/Product-Datasheets/SRR1280.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/infineon-technologies/BSS316NH6327XTSA1/2783469?s=N4IgTCBcDaIEIGUEGYCMA2AcgCXcsA7ABoAqCAgqiALoC%2BQA</t>
+  </si>
+  <si>
+    <t>https://www.infineon.com/assets/row/public/documents/24/49/infineon-bss316n-ds-en.pdf?folderId=db3a3043156fd573011622e10b5c1f67&amp;fileId=db3a304330f686060130ff7ee4b07f16</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/goford-semiconductor/G2K3N10L6/17112571</t>
+  </si>
+  <si>
+    <t>Bestückt wurde alter MOSFET: NTTFS6H888NLTAG (100Stk 33.79€)</t>
+  </si>
+  <si>
+    <t>https://www.gofordsemi.com/upload/cn/propdf/G2K3N10L6.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/yageo/RC0805FR-104K7L/13694155?s=N4IgTCBcDaIEoGEAMAOJBWAYnAtARiQBYBpAdgBkQBdAXyA</t>
+  </si>
+  <si>
+    <t>https://yageogroup.com/content/datasheet/asset/file/PYU-RC_GROUP_51_ROHS_L</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/yageo/RC0805JR-071ML/728219?s=N4IgTCBcDaIEoGEAMAOJBWAUnAtEg7AIwCyAMiALoC%2BQA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/yageo/RC0805FR-07100KL/727544?s=N4IgTCBcDaIEoGEAMAOJBWAYnAtEg7AIxJIDSAMiALoC%2BQA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/yageo/RC0805FR-13120RL/14286739?s=N4IgTCBcDaIEoGEAMAOJBWAYnAtARgGY8wk4AZEAXQF8g</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/te-connectivity-passive-product/CRG0805F2K2/2135487?s=N4IgTCBcDaIMICUDiAGAHCgrAMTAaQgF0BfIA</t>
+  </si>
+  <si>
+    <t>https://www.te.com/commerce/DocumentDelivery/DDEController?Action=srchrtrv&amp;DocNm=1773204&amp;DocType=Data%20Sheet&amp;DocLang=English&amp;DocFormat=pdf&amp;PartCntxt=4-1622826-1</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/yageo/AC0805FR-07200KL/5896661?s=N4IgTCBcDaIIIGEAMAOJBWAYgJQLRIHYwkkBpAGRAF0BfIA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/vishay-dale/CRCW080510R0FKEA/1175409</t>
+  </si>
+  <si>
+    <t>https://www.vishay.com/docs/20035/dcrcwe3.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/te-connectivity-passive-product/CRG0805F390R/2380897?s=N4IgTCBcDaIMICUDiAGAHCgrAMQMwE4UEQBdAXyA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/yageo/RC0805FR-07330RL/727866?s=N4IgTCBcDaIEoGEAMAOJBWAYnAtEg7AMyFJwAyIAugL5A</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/isabellenhuette-usa/CMP-R100-1-0/16836735</t>
+  </si>
+  <si>
+    <t>https://www.isabellenhuette.com/hubfs/files/Data%20sheets/CMP.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/panasonic-industry/ERA-6AEB203V/1465780?s=N4IgTCBcDaIKICUCCBaAbEuAhMAGAzAGogC6AvkA</t>
+  </si>
+  <si>
+    <t>https://industrial.panasonic.com/cdbs/www-data/pdf/RDM0000/AOA0000C307.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/yageo/RC0805FR-0710KL/727535?s=N4IgTCBcDaIEoGEAMAOJBWAYnAtEg7AIxIDSAMiALoC%2BQA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/yageo/RC0805FR-071KL/727444?s=N4IgTCBcDaIEoGEAMAOJBWAYnAtEg7AIwDSAMiALoC%2BQA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/yageo/RC0805FR-0720RL/727719?s=N4IgTCBcDaIEoGEAMAOJBWAYnAtEg7GEnADIgC6AvkA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/yageo/RC0805FR-07806RL/728162?s=N4IgTCBcDaIEoGEAMAOJBWAYnAtEg7GgGxwAyIAugL5A</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/yageo/RC0805FR-072K4L/727690</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/yageo/RC0805JR-070RL/728216</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/onsemi/RFP12N10L/458764?s=N4IgTCBcDaIEoDEAKBGMA5FAGAMiAugL5A</t>
+  </si>
+  <si>
+    <t>https://www.onsemi.com/pdf/datasheet/rfp12n10l-d.pdf</t>
+  </si>
+  <si>
+    <t>Ein-/Aus-Schalter</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/analog-devices-inc/ADUM1250ARZ-RL7/1240292?s=N4IgTCBcDaIIIBECqBZAjGArABjgJQC0BaPAGQHYQBdAXyA</t>
+  </si>
+  <si>
+    <t>I2C-ISO-Koppler</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/texas-instruments/SN65HVD233QDRQ1/6205566?s=N4IgTCBcDaIMoDkBsBWAEgNQCJgMy4EUsAlAgRhAF0BfIA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/mean-well-usa-inc/SCW20C-12/11482205?s=N4IgTCBcDaIMoGEDqYAMCC0BGCBdAvkA</t>
+  </si>
+  <si>
+    <t>CAN-Transceiver</t>
+  </si>
+  <si>
+    <t>https://www.meanwellusa.com/upload/pdf/SCW20/SCW20-spec.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/cincon-electronics-co-ltd/EC1SA16N/9682264</t>
+  </si>
+  <si>
+    <t>12V- Versorgung</t>
+  </si>
+  <si>
+    <t>5V+- Versorgung</t>
+  </si>
+  <si>
+    <t>https://www.cincon.com/productdownload/Datasheet-EC1SAN.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/texas-instruments/PCA9306DCUR/768359</t>
+  </si>
+  <si>
+    <t>I2C-Pegelwandler momentan als VSSOP8-Footprint - beides bestellt worden - auf Footprint achten</t>
+  </si>
+  <si>
+    <t>Ursprünglich PCF8575DBR genutzt, durch diesen ausgetauscht. Siehe Bericht</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/texas-instruments/PCF8575CDB/1573142</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/texas-instruments/LM1117IMPX-3-3-NOPB/1870906?s=N4IgTCBcDaIDIFkCMKDsBJBAFAGgWgGYA6AgegDkB5LAIRAF0BfIA</t>
+  </si>
+  <si>
+    <t>3.3V-Versorung</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/microchip-technology/MCP4725A0T-E-CH/1818537?s=N4IgTCBcDaILIGEAKAWA7GArAQQAwBUBaAUQHoEAJEAXQF8g</t>
+  </si>
+  <si>
+    <t>DAC - Digital-Analog-Wandler</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/liteon/LTV-847S-BC/17879250?s=N4IgTCBcDaIDIBUBqBaAHAFgOwGUUCEBhEAXQF8g</t>
+  </si>
+  <si>
+    <t>https://optoelectronics.liteon.com/upload/download/ds-70-96-0016/ltv-8x7%20series%20201610%20.pdf</t>
+  </si>
+  <si>
+    <t>Optokoppler</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/texas-instruments/TL084HIDR/13577753?s=N4IgTCBcDaICoBkAMAOALACQJIBEBKIAugL5A</t>
+  </si>
+  <si>
+    <t>OPV-4Fach</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/texas-instruments/LM2596T-ADJ/3701228</t>
+  </si>
+  <si>
+    <t>Laderegler</t>
+  </si>
+  <si>
+    <t>Stand: 24.09.2026</t>
   </si>
 </sst>
 </file>
@@ -778,8 +943,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FF99C66-B9A5-4B58-9A2D-91EE9E944E95}" name="Aktive_Bal_Doppelmosfet" displayName="Aktive_Bal_Doppelmosfet" ref="A1:M55" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:M55" xr:uid="{5FF99C66-B9A5-4B58-9A2D-91EE9E944E95}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FF99C66-B9A5-4B58-9A2D-91EE9E944E95}" name="Aktive_Bal_Doppelmosfet" displayName="Aktive_Bal_Doppelmosfet" ref="A1:M56" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:M56" xr:uid="{5FF99C66-B9A5-4B58-9A2D-91EE9E944E95}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{8245B2B7-4876-4526-87C1-E7CF70920112}" uniqueName="1" name="Reference" queryTableFieldId="1" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{981E7317-D2AF-408E-8673-F2F6BCB12F70}" uniqueName="2" name="Qty" queryTableFieldId="2"/>
@@ -1116,7 +1281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C70F1DE3-F6FC-4523-A997-2EF5AF24F92B}">
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="80.7265625" bestFit="1" customWidth="1"/>
@@ -1159,19 +1324,19 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="K1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="L1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="M1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -1197,7 +1362,7 @@
         <v>11</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I2" s="1">
         <v>20</v>
@@ -1209,7 +1374,7 @@
         <v>0.04</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="M2" s="1"/>
     </row>
@@ -1236,7 +1401,7 @@
         <v>11</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I3" s="1">
         <v>50</v>
@@ -1248,7 +1413,7 @@
         <v>1.153E-2</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="M3" s="1"/>
     </row>
@@ -1275,7 +1440,7 @@
         <v>11</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I4" s="1">
         <v>10</v>
@@ -1287,7 +1452,7 @@
         <v>0.15</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="M4" s="1"/>
     </row>
@@ -1314,7 +1479,7 @@
         <v>18</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I5" s="1">
         <v>10</v>
@@ -1326,7 +1491,7 @@
         <v>9.1090000000000004E-2</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="M5" s="1"/>
     </row>
@@ -1353,7 +1518,7 @@
         <v>11</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I6" s="1">
         <v>10</v>
@@ -1365,7 +1530,7 @@
         <v>1.298E-2</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M6" s="1"/>
     </row>
@@ -1392,7 +1557,7 @@
         <v>11</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I7" s="1">
         <v>2</v>
@@ -1404,7 +1569,7 @@
         <v>2.3429999999999999E-2</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="M7" s="1"/>
     </row>
@@ -1431,7 +1596,7 @@
         <v>18</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -1443,10 +1608,10 @@
         <v>1.09226</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -1472,7 +1637,7 @@
         <v>11</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I9" s="1">
         <v>10</v>
@@ -1484,7 +1649,7 @@
         <v>0.33673999999999998</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M9" s="1"/>
     </row>
@@ -1511,7 +1676,7 @@
         <v>11</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I10" s="1">
         <v>10</v>
@@ -1523,7 +1688,7 @@
         <v>5.8380000000000001E-2</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="M10" s="1"/>
     </row>
@@ -1550,7 +1715,7 @@
         <v>11</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I11" s="1">
         <v>10</v>
@@ -1562,7 +1727,7 @@
         <v>2.375E-2</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="M11" s="1"/>
     </row>
@@ -1589,7 +1754,7 @@
         <v>32</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I12" s="1">
         <v>2</v>
@@ -1601,10 +1766,10 @@
         <v>0.23305999999999999</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -1630,7 +1795,7 @@
         <v>11</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I13" s="1">
         <v>10</v>
@@ -1642,7 +1807,7 @@
         <v>2.332E-2</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="M13" s="1"/>
     </row>
@@ -1669,7 +1834,7 @@
         <v>37</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I14">
         <v>2</v>
@@ -1681,7 +1846,7 @@
         <v>9.4579999999999997E-2</v>
       </c>
       <c r="L14" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M14" s="1"/>
     </row>
@@ -1708,7 +1873,7 @@
         <v>40</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I15" s="1">
         <v>2</v>
@@ -1720,7 +1885,7 @@
         <v>3.17</v>
       </c>
       <c r="L15" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="M15" s="1"/>
     </row>
@@ -1747,7 +1912,7 @@
         <v>43</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I16" s="1">
         <v>2</v>
@@ -1759,7 +1924,7 @@
         <v>0.22717999999999999</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M16" s="1"/>
     </row>
@@ -1786,7 +1951,7 @@
         <v>46</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I17" s="1">
         <v>2</v>
@@ -1798,7 +1963,7 @@
         <v>0.37917000000000001</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="M17" s="1"/>
     </row>
@@ -1825,7 +1990,7 @@
         <v>49</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I18" s="1">
         <v>20</v>
@@ -1837,7 +2002,7 @@
         <v>0.12018</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="M18" s="1"/>
     </row>
@@ -1864,7 +2029,7 @@
         <v>52</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I19" s="1">
         <v>5</v>
@@ -1876,7 +2041,7 @@
         <v>0.3</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M19" s="1"/>
     </row>
@@ -1903,7 +2068,7 @@
         <v>55</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I20" s="1">
         <v>12</v>
@@ -1915,7 +2080,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M20" s="1"/>
     </row>
@@ -1942,7 +2107,7 @@
         <v>49</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I21" s="1">
         <v>1</v>
@@ -1954,7 +2119,7 @@
         <v>0.3</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M21" s="1"/>
     </row>
@@ -1981,7 +2146,7 @@
         <v>49</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I22" s="1">
         <v>1</v>
@@ -1993,7 +2158,7 @@
         <v>0.3</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M22" s="1"/>
     </row>
@@ -2020,7 +2185,7 @@
         <v>61</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I23" s="1">
         <v>2</v>
@@ -2032,7 +2197,7 @@
         <v>0.128</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M23" s="1"/>
     </row>
@@ -2059,12 +2224,20 @@
         <v>63</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
+        <v>196</v>
+      </c>
+      <c r="I24" s="1">
+        <v>2</v>
+      </c>
+      <c r="J24" s="2">
+        <v>1.98</v>
+      </c>
+      <c r="K24" s="2">
+        <v>0.63300000000000001</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>195</v>
+      </c>
       <c r="M24" s="1"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
@@ -2089,13 +2262,21 @@
       <c r="G25" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
+      <c r="H25" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="I25" s="1">
+        <v>2</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0.52</v>
+      </c>
+      <c r="K25" s="2">
+        <v>6.2399999999999997E-2</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>197</v>
+      </c>
       <c r="M25" s="1"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
@@ -2121,13 +2302,23 @@
         <v>69</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
+        <v>201</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0.106</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
@@ -2151,13 +2342,21 @@
       <c r="G27" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
+      <c r="H27" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="I27" s="1">
+        <v>10</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="K27" s="2">
+        <v>5.4799999999999996E-3</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="M27" s="1"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
@@ -2183,12 +2382,20 @@
         <v>72</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
+        <v>203</v>
+      </c>
+      <c r="I28" s="1">
+        <v>10</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="K28" s="2">
+        <v>5.4799999999999996E-3</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="M28" s="1"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
@@ -2214,12 +2421,20 @@
         <v>72</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
+        <v>203</v>
+      </c>
+      <c r="I29" s="1">
+        <v>100</v>
+      </c>
+      <c r="J29" s="2">
+        <v>1.45</v>
+      </c>
+      <c r="K29" s="2">
+        <v>5.4799999999999996E-3</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>205</v>
+      </c>
       <c r="M29" s="1"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
@@ -2245,12 +2460,20 @@
         <v>72</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
+        <v>203</v>
+      </c>
+      <c r="I30" s="1">
+        <v>2</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="K30" s="2">
+        <v>4.9800000000000001E-3</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>206</v>
+      </c>
       <c r="M30" s="1"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
@@ -2276,12 +2499,20 @@
         <v>72</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
+        <v>208</v>
+      </c>
+      <c r="I31" s="1">
+        <v>10</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0.32</v>
+      </c>
+      <c r="K31" s="2">
+        <v>8.6199999999999992E-3</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>207</v>
+      </c>
       <c r="M31" s="1"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">
@@ -2307,12 +2538,20 @@
         <v>72</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
+        <v>203</v>
+      </c>
+      <c r="I32" s="1">
+        <v>2</v>
+      </c>
+      <c r="J32" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="K32" s="2">
+        <v>4.9800000000000001E-3</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>209</v>
+      </c>
       <c r="M32" s="1"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.35">
@@ -2338,12 +2577,20 @@
         <v>72</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
+        <v>211</v>
+      </c>
+      <c r="I33" s="1">
+        <v>2</v>
+      </c>
+      <c r="J33" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="K33" s="2">
+        <v>4.9800000000000001E-3</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="M33" s="1"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.35">
@@ -2369,12 +2616,20 @@
         <v>72</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
+        <v>208</v>
+      </c>
+      <c r="I34" s="1">
+        <v>50</v>
+      </c>
+      <c r="J34" s="2">
+        <v>0.99</v>
+      </c>
+      <c r="K34" s="2">
+        <v>8.1300000000000001E-3</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>212</v>
+      </c>
       <c r="M34" s="1"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.35">
@@ -2400,12 +2655,20 @@
         <v>72</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
+        <v>203</v>
+      </c>
+      <c r="I35" s="1">
+        <v>100</v>
+      </c>
+      <c r="J35" s="2">
+        <v>1.45</v>
+      </c>
+      <c r="K35" s="2">
+        <v>6.1199999999999996E-3</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>213</v>
+      </c>
       <c r="M35" s="1"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.35">
@@ -2431,12 +2694,20 @@
         <v>91</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
+        <v>215</v>
+      </c>
+      <c r="I36" s="1">
+        <v>2</v>
+      </c>
+      <c r="J36" s="2">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="K36" s="2">
+        <v>0.308</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>214</v>
+      </c>
       <c r="M36" s="1"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.35">
@@ -2462,12 +2733,20 @@
         <v>72</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
+        <v>217</v>
+      </c>
+      <c r="I37" s="1">
+        <v>10</v>
+      </c>
+      <c r="J37" s="2">
+        <v>0.59</v>
+      </c>
+      <c r="K37" s="2">
+        <v>4.2709999999999998E-2</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="M37" s="1"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.35">
@@ -2493,12 +2772,20 @@
         <v>72</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
+        <v>203</v>
+      </c>
+      <c r="I38" s="1">
+        <v>50</v>
+      </c>
+      <c r="J38" s="2">
+        <v>0.81</v>
+      </c>
+      <c r="K38" s="2">
+        <v>6.1199999999999996E-3</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>218</v>
+      </c>
       <c r="M38" s="1"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.35">
@@ -2524,12 +2811,20 @@
         <v>72</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
+        <v>203</v>
+      </c>
+      <c r="I39" s="1">
+        <v>10</v>
+      </c>
+      <c r="J39" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="K39" s="2">
+        <v>6.1199999999999996E-3</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>219</v>
+      </c>
       <c r="M39" s="1"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.35">
@@ -2555,12 +2850,20 @@
         <v>72</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
+        <v>203</v>
+      </c>
+      <c r="I40" s="1">
+        <v>10</v>
+      </c>
+      <c r="J40" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="K40" s="2">
+        <v>6.4900000000000001E-3</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>220</v>
+      </c>
       <c r="M40" s="1"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.35">
@@ -2586,12 +2889,20 @@
         <v>72</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
+        <v>203</v>
+      </c>
+      <c r="I41" s="1">
+        <v>2</v>
+      </c>
+      <c r="J41" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="K41" s="2">
+        <v>6.1199999999999996E-3</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>221</v>
+      </c>
       <c r="M41" s="1"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.35">
@@ -2617,12 +2928,20 @@
         <v>72</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
+        <v>203</v>
+      </c>
+      <c r="I42" s="1">
+        <v>2</v>
+      </c>
+      <c r="J42" s="2">
+        <v>0.18</v>
+      </c>
+      <c r="K42" s="2">
+        <v>6.1199999999999996E-3</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>222</v>
+      </c>
       <c r="M42" s="1"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.35">
@@ -2648,12 +2967,20 @@
         <v>72</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
+        <v>203</v>
+      </c>
+      <c r="I43" s="1">
+        <v>10</v>
+      </c>
+      <c r="J43" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="K43" s="2">
+        <v>5.2300000000000003E-3</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>223</v>
+      </c>
       <c r="M43" s="1"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.35">
@@ -2679,13 +3006,23 @@
         <v>108</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
+        <v>225</v>
+      </c>
+      <c r="I44" s="1">
+        <v>2</v>
+      </c>
+      <c r="J44" s="2">
+        <v>3.04</v>
+      </c>
+      <c r="K44" s="2">
+        <v>0.70328000000000002</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
@@ -2712,11 +3049,21 @@
       <c r="H45" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
+      <c r="I45" s="1">
+        <v>2</v>
+      </c>
+      <c r="J45" s="2">
+        <v>12.8</v>
+      </c>
+      <c r="K45" s="2">
+        <v>4.18</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
@@ -2743,11 +3090,21 @@
       <c r="H46" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
+      <c r="I46" s="1">
+        <v>2</v>
+      </c>
+      <c r="J46" s="2">
+        <v>6.32</v>
+      </c>
+      <c r="K46" s="2">
+        <v>1.8049999999999999</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
@@ -2771,148 +3128,198 @@
       <c r="G47" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="H47" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
+      <c r="H47" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="I47" s="1">
+        <v>2</v>
+      </c>
+      <c r="J47" s="2">
+        <v>32.72</v>
+      </c>
+      <c r="K47" s="2">
+        <v>17.45</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B48">
-        <v>1</v>
-      </c>
-      <c r="C48" s="1" t="s">
+      <c r="D48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="H48" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="I48" s="1">
+        <v>2</v>
+      </c>
+      <c r="J48" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="K48" s="2">
+        <v>5.9139999999999997</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B49">
-        <v>1</v>
-      </c>
-      <c r="C49" s="1" t="s">
+      <c r="H49" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
+      <c r="I49" s="1">
+        <v>2</v>
+      </c>
+      <c r="J49" s="2">
+        <v>1.56</v>
+      </c>
+      <c r="K49" s="2">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B50">
-        <v>1</v>
-      </c>
-      <c r="C50" s="1" t="s">
+      <c r="H50" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
+      <c r="I50" s="1">
+        <v>2</v>
+      </c>
+      <c r="J50" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="K50" s="2">
+        <v>3.8969999999999998</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B51">
-        <v>1</v>
-      </c>
-      <c r="C51" s="1" t="s">
+      <c r="H51" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
+      <c r="I51" s="1">
+        <v>2</v>
+      </c>
+      <c r="J51" s="2">
+        <v>1.82</v>
+      </c>
+      <c r="K51" s="2">
+        <v>0.505</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>10</v>
@@ -2927,23 +3334,33 @@
         <v>69</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
+        <v>137</v>
+      </c>
+      <c r="I52" s="1">
+        <v>2</v>
+      </c>
+      <c r="J52" s="2">
+        <v>2.16</v>
+      </c>
+      <c r="K52" s="2">
+        <v>0.83</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="M52" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B53">
         <v>4</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>10</v>
@@ -2955,78 +3372,124 @@
         <v>10</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
-      <c r="M53" s="1"/>
+        <v>140</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="I53" s="1">
+        <v>10</v>
+      </c>
+      <c r="J53" s="2">
+        <v>8.4700000000000006</v>
+      </c>
+      <c r="K53" s="2">
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H54" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B54">
-        <v>1</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
-      <c r="M54" s="1"/>
+      <c r="I54" s="1">
+        <v>2</v>
+      </c>
+      <c r="J54" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="K54" s="2">
+        <v>0.128</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H55" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B55">
-        <v>1</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
-      <c r="M55" s="1"/>
+      <c r="I55" s="1">
+        <v>2</v>
+      </c>
+      <c r="J55" s="2">
+        <v>12.52</v>
+      </c>
+      <c r="K55" s="2">
+        <v>3.7109999999999999</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3039,10 +3502,16 @@
     <hyperlink ref="L19" r:id="rId7" xr:uid="{EC612383-17BE-4B44-B2ED-1B82FB019128}"/>
     <hyperlink ref="L21" r:id="rId8" xr:uid="{FE7EC3EF-4FA4-4C36-BA3D-754D087BC864}"/>
     <hyperlink ref="L22" r:id="rId9" xr:uid="{79CA8F48-A562-40AB-920C-FEB1BE5784DB}"/>
+    <hyperlink ref="H25" r:id="rId10" xr:uid="{75417169-CE60-4822-BB28-DE45313BB079}"/>
+    <hyperlink ref="H27" r:id="rId11" xr:uid="{4FBD5120-40E8-4DC4-A0A5-5EDE5E76C128}"/>
+    <hyperlink ref="H47" r:id="rId12" xr:uid="{87A351C1-92A8-44F0-B31F-F705446157D3}"/>
+    <hyperlink ref="H53" r:id="rId13" xr:uid="{9942414F-CB78-43EF-9F9A-A408BAD52A82}"/>
+    <hyperlink ref="H55" r:id="rId14" xr:uid="{9E2FF9D3-D9B9-484C-860A-D912EB715736}"/>
+    <hyperlink ref="H54" r:id="rId15" xr:uid="{18B064F2-C559-4148-A4B8-985415078C5E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId10"/>
+    <tablePart r:id="rId16"/>
   </tableParts>
 </worksheet>
 </file>
